--- a/Yosys_PNR_Icepack_Iceprog.xlsx
+++ b/Yosys_PNR_Icepack_Iceprog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harrisonwarke/Documents/FPGA Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE8C7AFC-54CF-5F4C-A4A5-E3CFB9B4657C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0494C07-3CF2-BF40-A3C7-01A6BB637FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{B5ED1AD9-680E-6146-9023-A0DDD4422510}"/>
   </bookViews>
@@ -911,7 +911,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
